--- a/data/trans_dic/MCS12_SP_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,42; 36,62</t>
+          <t>28,09; 36,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,92; 39,75</t>
+          <t>30,61; 39,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 38,42</t>
+          <t>29,11; 38,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 33,73</t>
+          <t>18,84; 34,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,21; 47,15</t>
+          <t>38,43; 47,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,41; 53,93</t>
+          <t>44,65; 54,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,19</t>
+          <t>39,41; 49,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,76; 46,91</t>
+          <t>32,01; 46,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,46; 40,57</t>
+          <t>34,39; 40,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,75; 45,45</t>
+          <t>38,77; 45,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 42,08</t>
+          <t>35,31; 42,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,45; 37,81</t>
+          <t>26,48; 37,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,74; 37,91</t>
+          <t>31,4; 38,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,59; 48,39</t>
+          <t>40,72; 48,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,01; 49,94</t>
+          <t>41,54; 49,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,18; 39,91</t>
+          <t>27,9; 40,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,7; 52,99</t>
+          <t>44,52; 52,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,46; 59,68</t>
+          <t>51,28; 59,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,53; 52,99</t>
+          <t>45,35; 53,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,0; 67,87</t>
+          <t>38,0; 67,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,68</t>
+          <t>38,52; 43,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,85; 52,62</t>
+          <t>46,76; 52,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,58; 50,63</t>
+          <t>44,45; 50,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,63; 55,13</t>
+          <t>35,19; 56,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,79; 47,34</t>
+          <t>39,5; 47,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,95; 54,62</t>
+          <t>46,92; 54,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,17; 51,85</t>
+          <t>44,14; 51,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,75; 40,3</t>
+          <t>31,45; 40,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,31; 61,97</t>
+          <t>54,18; 62,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,77; 67,36</t>
+          <t>59,67; 67,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,5; 53,35</t>
+          <t>45,91; 53,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,56; 47,29</t>
+          <t>40,75; 47,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,23; 53,91</t>
+          <t>48,75; 53,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54,45; 60,14</t>
+          <t>54,57; 60,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,8; 51,33</t>
+          <t>46,33; 51,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,32; 43,02</t>
+          <t>37,44; 42,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,63; 49,44</t>
+          <t>40,76; 49,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,34; 58,11</t>
+          <t>49,46; 57,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,46; 57,63</t>
+          <t>49,01; 57,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 45,71</t>
+          <t>12,85; 45,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,98; 66,61</t>
+          <t>58,23; 66,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,75; 68,01</t>
+          <t>60,15; 68,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,54; 64,3</t>
+          <t>56,3; 64,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,71; 53,72</t>
+          <t>41,36; 53,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,54; 56,91</t>
+          <t>50,47; 56,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,05; 61,98</t>
+          <t>56,37; 61,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,22; 59,67</t>
+          <t>54,28; 59,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,68; 48,0</t>
+          <t>22,8; 48,01</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,13; 61,19</t>
+          <t>50,99; 61,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,15; 60,16</t>
+          <t>49,74; 59,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,82; 56,44</t>
+          <t>47,14; 56,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,78; 52,93</t>
+          <t>45,55; 53,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,07; 63,85</t>
+          <t>54,17; 63,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,65; 73,16</t>
+          <t>64,11; 73,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,16; 66,71</t>
+          <t>57,38; 66,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,81; 59,99</t>
+          <t>53,92; 60,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,63; 60,78</t>
+          <t>54,01; 61,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,48; 65,11</t>
+          <t>58,76; 65,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,81; 60,56</t>
+          <t>53,65; 60,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,49; 55,86</t>
+          <t>50,55; 55,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,75; 59,86</t>
+          <t>48,37; 60,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,24; 56,39</t>
+          <t>44,67; 56,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,11; 56,47</t>
+          <t>45,14; 56,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,32; 52,94</t>
+          <t>45,15; 53,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,17; 62,02</t>
+          <t>51,66; 61,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,81; 69,65</t>
+          <t>59,65; 69,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,61; 63,73</t>
+          <t>53,51; 64,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,58; 87,24</t>
+          <t>53,7; 87,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,11; 59,49</t>
+          <t>52,21; 59,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54,37; 62,37</t>
+          <t>53,79; 61,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,19; 59,03</t>
+          <t>51,1; 58,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51,3; 79,12</t>
+          <t>51,3; 79,52</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48,48; 61,23</t>
+          <t>47,62; 61,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,68; 64,3</t>
+          <t>50,48; 63,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,26; 59,66</t>
+          <t>48,24; 59,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,97; 60,19</t>
+          <t>50,6; 59,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,79; 56,23</t>
+          <t>44,97; 55,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,26; 72,8</t>
+          <t>63,18; 73,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,4; 65,66</t>
+          <t>55,02; 65,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,41; 66,92</t>
+          <t>60,34; 67,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,8; 56,37</t>
+          <t>48,0; 56,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,88; 67,77</t>
+          <t>59,6; 68,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53,72; 61,76</t>
+          <t>54,08; 62,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,53; 63,05</t>
+          <t>57,61; 63,21</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,41; 44,98</t>
+          <t>41,49; 45,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,28; 50,73</t>
+          <t>47,31; 50,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,4; 49,84</t>
+          <t>46,51; 50,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,37; 42,04</t>
+          <t>30,56; 42,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,47; 55,94</t>
+          <t>52,4; 56,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,19; 63,49</t>
+          <t>60,17; 63,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,1; 56,57</t>
+          <t>53,18; 56,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,04; 61,56</t>
+          <t>50,15; 62,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47,59; 50,01</t>
+          <t>47,47; 49,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,27; 56,69</t>
+          <t>54,39; 56,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50,42; 52,82</t>
+          <t>50,21; 52,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,95; 50,83</t>
+          <t>41,94; 51,27</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>140429; 180921</t>
+          <t>138800; 179080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>140438; 180513</t>
+          <t>139018; 181152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121804; 161168</t>
+          <t>122091; 162265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76018; 134921</t>
+          <t>75360; 136260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>178646; 220414</t>
+          <t>179663; 220539</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>191075; 232027</t>
+          <t>192100; 233165</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155671; 194672</t>
+          <t>155963; 194178</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>98972; 146168</t>
+          <t>99749; 145793</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>331308; 390130</t>
+          <t>330703; 390176</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342731; 401964</t>
+          <t>342855; 400277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>285171; 343066</t>
+          <t>287852; 344430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>188204; 269073</t>
+          <t>188438; 266099</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>226060; 278843</t>
+          <t>230931; 280456</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>278908; 332454</t>
+          <t>279757; 334066</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248080; 294905</t>
+          <t>245315; 295141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119350; 169021</t>
+          <t>118149; 169830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>279582; 331441</t>
+          <t>278497; 329391</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>314021; 364228</t>
+          <t>312935; 364796</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>250945; 298620</t>
+          <t>255547; 301731</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>194175; 346776</t>
+          <t>194192; 346211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>519621; 594422</t>
+          <t>524290; 595734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>607766; 682615</t>
+          <t>606594; 680481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514523; 584234</t>
+          <t>513006; 583283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>332972; 515184</t>
+          <t>328868; 526946</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>254122; 302328</t>
+          <t>252290; 306203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>320139; 372448</t>
+          <t>319946; 374084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>295524; 346899</t>
+          <t>295334; 347309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169975; 215779</t>
+          <t>168353; 215353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>374629; 427406</t>
+          <t>373700; 428926</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>424844; 478815</t>
+          <t>424174; 481088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>300904; 352862</t>
+          <t>303618; 353462</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>219712; 256218</t>
+          <t>220768; 258457</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>640673; 716116</t>
+          <t>647623; 715925</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>758290; 837582</t>
+          <t>760064; 836641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>609309; 682872</t>
+          <t>616430; 688838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>402009; 463331</t>
+          <t>403244; 462862</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>210914; 256654</t>
+          <t>211625; 257941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>303279; 357153</t>
+          <t>303973; 356194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>319546; 372329</t>
+          <t>316646; 370428</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120392; 404851</t>
+          <t>113836; 400140</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>298972; 343456</t>
+          <t>300237; 344864</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>368154; 419090</t>
+          <t>370624; 420476</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>366991; 417327</t>
+          <t>365429; 417768</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>295832; 381070</t>
+          <t>293405; 379934</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>522955; 588922</t>
+          <t>522273; 587914</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>689841; 762897</t>
+          <t>693855; 762624</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>702194; 772804</t>
+          <t>702970; 771865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>361775; 765610</t>
+          <t>363716; 765739</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>197741; 236626</t>
+          <t>197201; 238022</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215348; 258342</t>
+          <t>213603; 257552</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223775; 269732</t>
+          <t>225274; 270554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248523; 293722</t>
+          <t>252777; 297560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>218454; 257927</t>
+          <t>218838; 258174</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285006; 327626</t>
+          <t>287071; 326885</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>283991; 331472</t>
+          <t>285069; 330476</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>293567; 327291</t>
+          <t>294172; 328192</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>424081; 480553</t>
+          <t>427016; 484017</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>513006; 571204</t>
+          <t>515417; 575818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>524551; 590319</t>
+          <t>522993; 587031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>555672; 614742</t>
+          <t>556364; 615933</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>139721; 175148</t>
+          <t>141528; 175895</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>137063; 174701</t>
+          <t>138375; 175511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150808; 188806</t>
+          <t>150916; 187435</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>161215; 192558</t>
+          <t>164252; 192836</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>178894; 212688</t>
+          <t>177176; 211622</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>211708; 246566</t>
+          <t>211167; 247537</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>202519; 240738</t>
+          <t>202157; 242883</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>325047; 529222</t>
+          <t>325757; 533218</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>331142; 378096</t>
+          <t>331835; 380219</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>360931; 414002</t>
+          <t>357055; 409963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>364485; 420346</t>
+          <t>363905; 416815</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>497787; 767784</t>
+          <t>497780; 771703</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>101754; 128512</t>
+          <t>99940; 129291</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>126614; 160651</t>
+          <t>126117; 159348</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124036; 153326</t>
+          <t>123980; 152435</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142916; 168795</t>
+          <t>141896; 167007</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>149550; 187769</t>
+          <t>150156; 186824</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>246079; 283176</t>
+          <t>245740; 284163</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>217675; 262742</t>
+          <t>220157; 263281</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>252334; 279537</t>
+          <t>252066; 280404</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>259941; 306537</t>
+          <t>261032; 305440</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>382548; 432945</t>
+          <t>380763; 434373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>353023; 405896</t>
+          <t>355394; 409372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>401602; 440165</t>
+          <t>402190; 441283</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1356877; 1473889</t>
+          <t>1359326; 1474346</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1620190; 1738378</t>
+          <t>1621155; 1735304</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1575082; 1691855</t>
+          <t>1578751; 1701411</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>976902; 1447636</t>
+          <t>1052445; 1456307</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1773088; 1890301</t>
+          <t>1770768; 1893868</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2141823; 2259257</t>
+          <t>2141157; 2255406</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1882208; 2005086</t>
+          <t>1884984; 2012236</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1823309; 2243155</t>
+          <t>1827309; 2268094</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3167492; 3328852</t>
+          <t>3159395; 3321312</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3790831; 3959656</t>
+          <t>3799360; 3968661</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3498469; 3664912</t>
+          <t>3483912; 3659063</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2972898; 3602461</t>
+          <t>2972143; 3633796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,09; 36,25</t>
+          <t>27,9; 36,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,61; 39,89</t>
+          <t>30,96; 39,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 38,68</t>
+          <t>28,86; 38,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 34,07</t>
+          <t>22,48; 36,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,43; 47,18</t>
+          <t>38,46; 47,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,65; 54,2</t>
+          <t>44,02; 54,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,41; 49,07</t>
+          <t>39,12; 48,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,01; 46,79</t>
+          <t>30,14; 44,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,39; 40,58</t>
+          <t>34,44; 40,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,26</t>
+          <t>38,67; 45,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,31; 42,25</t>
+          <t>35,48; 42,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,48; 37,39</t>
+          <t>27,82; 37,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,13</t>
+          <t>30,88; 38,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,72; 48,62</t>
+          <t>40,4; 48,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,54; 49,98</t>
+          <t>41,81; 50,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,9; 40,1</t>
+          <t>28,91; 39,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,52; 52,66</t>
+          <t>44,54; 52,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,28; 59,78</t>
+          <t>51,18; 59,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,35; 53,54</t>
+          <t>45,24; 53,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,0; 67,76</t>
+          <t>35,76; 45,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,52; 43,77</t>
+          <t>38,4; 43,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,76; 52,45</t>
+          <t>46,93; 52,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,45; 50,54</t>
+          <t>44,47; 50,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 56,39</t>
+          <t>33,97; 41,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 47,94</t>
+          <t>39,3; 47,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,92; 54,86</t>
+          <t>46,74; 54,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,14; 51,91</t>
+          <t>44,05; 51,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,45; 40,23</t>
+          <t>32,44; 40,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,18; 62,19</t>
+          <t>54,41; 62,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,67; 67,68</t>
+          <t>59,84; 67,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,91; 53,44</t>
+          <t>45,72; 53,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,75; 47,71</t>
+          <t>42,22; 48,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,75; 53,89</t>
+          <t>48,4; 53,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54,57; 60,07</t>
+          <t>54,9; 60,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,33; 51,77</t>
+          <t>46,15; 51,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,44; 42,97</t>
+          <t>38,06; 43,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,76; 49,69</t>
+          <t>40,79; 49,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,46; 57,95</t>
+          <t>49,53; 58,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,01; 57,34</t>
+          <t>49,03; 57,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 45,18</t>
+          <t>39,44; 47,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,23; 66,88</t>
+          <t>58,39; 67,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,15; 68,24</t>
+          <t>59,76; 67,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,3; 64,36</t>
+          <t>56,92; 64,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,36; 53,56</t>
+          <t>48,93; 54,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,47; 56,81</t>
+          <t>50,71; 56,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,37; 61,96</t>
+          <t>56,16; 62,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,28; 59,6</t>
+          <t>54,1; 60,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 48,01</t>
+          <t>45,2; 50,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,99; 61,55</t>
+          <t>50,77; 60,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,74; 59,98</t>
+          <t>49,94; 59,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,14; 56,61</t>
+          <t>46,97; 56,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,55; 53,62</t>
+          <t>45,02; 52,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,17; 63,91</t>
+          <t>53,58; 63,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,11; 73,0</t>
+          <t>63,95; 73,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,38; 66,51</t>
+          <t>57,1; 66,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,92; 60,15</t>
+          <t>54,81; 60,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,01; 61,21</t>
+          <t>53,56; 60,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,76; 65,64</t>
+          <t>58,69; 65,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,65; 60,22</t>
+          <t>53,5; 60,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,55; 55,97</t>
+          <t>50,76; 55,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,37; 60,12</t>
+          <t>48,53; 59,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,67; 56,66</t>
+          <t>44,58; 56,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,14; 56,06</t>
+          <t>45,1; 56,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,15; 53,01</t>
+          <t>44,62; 52,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,66; 61,71</t>
+          <t>51,65; 62,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,65; 69,93</t>
+          <t>59,47; 69,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,51; 64,3</t>
+          <t>53,15; 63,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,7; 87,9</t>
+          <t>52,65; 59,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,21; 59,83</t>
+          <t>52,02; 59,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53,79; 61,76</t>
+          <t>54,24; 62,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,1; 58,53</t>
+          <t>51,01; 58,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51,3; 79,52</t>
+          <t>49,77; 55,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,62; 61,6</t>
+          <t>47,96; 61,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,48; 63,78</t>
+          <t>50,66; 63,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,24; 59,31</t>
+          <t>48,79; 60,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,6; 59,56</t>
+          <t>50,78; 60,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,97; 55,95</t>
+          <t>44,64; 56,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,18; 73,05</t>
+          <t>63,37; 73,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,02; 65,79</t>
+          <t>54,0; 65,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,34; 67,13</t>
+          <t>60,06; 66,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,0; 56,17</t>
+          <t>47,56; 56,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,6; 68,0</t>
+          <t>60,18; 67,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54,08; 62,29</t>
+          <t>53,64; 62,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,61; 63,21</t>
+          <t>57,9; 63,18</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,49; 45,0</t>
+          <t>41,5; 44,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,31; 50,64</t>
+          <t>47,21; 50,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,51; 50,12</t>
+          <t>46,25; 49,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,56; 42,29</t>
+          <t>40,03; 43,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,4; 56,04</t>
+          <t>52,49; 55,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,38</t>
+          <t>60,19; 63,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,18; 56,77</t>
+          <t>52,98; 56,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,15; 62,25</t>
+          <t>49,42; 52,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47,47; 49,9</t>
+          <t>47,5; 49,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,39; 56,82</t>
+          <t>54,36; 56,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50,21; 52,73</t>
+          <t>50,28; 52,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,94; 51,27</t>
+          <t>45,3; 47,61</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103184</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>122000</t>
+          <t>134510</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>225184</t>
+          <t>254016</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>138800; 179080</t>
+          <t>137843; 180292</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139018; 181152</t>
+          <t>140596; 180487</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122091; 162265</t>
+          <t>121056; 160777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75360; 136260</t>
+          <t>91665; 150230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>179663; 220539</t>
+          <t>179782; 222766</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>192100; 233165</t>
+          <t>189371; 233167</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155963; 194178</t>
+          <t>154804; 192580</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99749; 145793</t>
+          <t>108814; 159872</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>330703; 390176</t>
+          <t>331165; 389391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342855; 400277</t>
+          <t>341990; 400094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287852; 344430</t>
+          <t>289223; 343908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>188438; 266099</t>
+          <t>213888; 291944</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143406</t>
+          <t>163176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>244013</t>
+          <t>202386</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>387419</t>
+          <t>365563</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>230931; 280456</t>
+          <t>227107; 280295</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>279757; 334066</t>
+          <t>277615; 330008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245315; 295141</t>
+          <t>246900; 298066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>118149; 169830</t>
+          <t>137881; 188128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>278497; 329391</t>
+          <t>278570; 328298</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>312935; 364796</t>
+          <t>312304; 362451</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>255547; 301731</t>
+          <t>254935; 300356</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>194192; 346211</t>
+          <t>178989; 226262</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>524290; 595734</t>
+          <t>522622; 595768</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>606594; 680481</t>
+          <t>608855; 681480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513006; 583283</t>
+          <t>513177; 581563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>328868; 526946</t>
+          <t>332037; 401289</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193411</t>
+          <t>224126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>238605</t>
+          <t>282361</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>432016</t>
+          <t>506487</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>252290; 306203</t>
+          <t>250973; 303022</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>319946; 374084</t>
+          <t>318705; 374392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>295334; 347309</t>
+          <t>294706; 347701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>168353; 215353</t>
+          <t>201053; 249261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>373700; 428926</t>
+          <t>375300; 428003</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>424174; 481088</t>
+          <t>425379; 477949</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>303618; 353462</t>
+          <t>302355; 353405</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>220768; 258457</t>
+          <t>262323; 302472</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>647623; 715925</t>
+          <t>642892; 715756</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>760064; 836641</t>
+          <t>764577; 837246</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>616430; 688838</t>
+          <t>613987; 687198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>403244; 462862</t>
+          <t>472440; 538830</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283870</t>
+          <t>303351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>353174</t>
+          <t>381377</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>637044</t>
+          <t>684728</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211625; 257941</t>
+          <t>211777; 257436</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>303973; 356194</t>
+          <t>304442; 357375</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316646; 370428</t>
+          <t>316759; 369760</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113836; 400140</t>
+          <t>275502; 332627</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>300237; 344864</t>
+          <t>301075; 345651</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>370624; 420476</t>
+          <t>368213; 418009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>365429; 417768</t>
+          <t>369431; 417116</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>293405; 379934</t>
+          <t>358734; 403071</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>522273; 587914</t>
+          <t>524703; 586583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>693855; 762624</t>
+          <t>691214; 763369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>702970; 771865</t>
+          <t>700622; 777367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>363716; 765739</t>
+          <t>647141; 718157</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273344</t>
+          <t>294214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>310590</t>
+          <t>350506</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>583934</t>
+          <t>644720</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>197201; 238022</t>
+          <t>196328; 233367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>213603; 257552</t>
+          <t>214460; 256978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225274; 270554</t>
+          <t>224475; 271069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252777; 297560</t>
+          <t>271133; 316264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>218838; 258174</t>
+          <t>216436; 257961</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>287071; 326885</t>
+          <t>286366; 328452</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>285069; 330476</t>
+          <t>283720; 328304</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>294172; 328192</t>
+          <t>332434; 369223</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>427016; 484017</t>
+          <t>423514; 480745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>515417; 575818</t>
+          <t>514823; 573943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>522993; 587031</t>
+          <t>521531; 588798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>556364; 615933</t>
+          <t>613606; 673988</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178299</t>
+          <t>195363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>425624</t>
+          <t>244552</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>603923</t>
+          <t>439915</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>141528; 175895</t>
+          <t>141986; 174144</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>138375; 175511</t>
+          <t>138096; 173865</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150916; 187435</t>
+          <t>150768; 188710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164252; 192836</t>
+          <t>179424; 212530</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>177176; 211622</t>
+          <t>177121; 213645</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>211167; 247537</t>
+          <t>210511; 247228</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>202157; 242883</t>
+          <t>200771; 241285</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>325757; 533218</t>
+          <t>230228; 259688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>331835; 380219</t>
+          <t>330590; 377421</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>357055; 409963</t>
+          <t>360064; 413925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>363905; 416815</t>
+          <t>363268; 415425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>497780; 771703</t>
+          <t>417774; 462403</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155029</t>
+          <t>171245</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>266424</t>
+          <t>290495</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>421453</t>
+          <t>461740</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>99940; 129291</t>
+          <t>100657; 128202</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>126117; 159348</t>
+          <t>126568; 159290</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123980; 152435</t>
+          <t>125402; 154896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>141896; 167007</t>
+          <t>156194; 185856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>150156; 186824</t>
+          <t>149060; 188759</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>245740; 284163</t>
+          <t>246499; 284638</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>220157; 263281</t>
+          <t>216093; 264018</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>252066; 280404</t>
+          <t>273786; 305306</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>261032; 305440</t>
+          <t>258652; 306175</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>380763; 434373</t>
+          <t>384432; 432442</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>355394; 409372</t>
+          <t>352485; 408592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>402190; 441283</t>
+          <t>441995; 482305</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1359326; 1474346</t>
+          <t>1359732; 1472819</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1621155; 1735304</t>
+          <t>1617919; 1741217</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1578751; 1701411</t>
+          <t>1569963; 1684833</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1052445; 1456307</t>
+          <t>1407074; 1533452</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1770768; 1893868</t>
+          <t>1773654; 1890895</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2141157; 2255406</t>
+          <t>2141732; 2263726</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1884984; 2012236</t>
+          <t>1877885; 2002874</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1827309; 2268094</t>
+          <t>1836258; 1940212</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3159395; 3321312</t>
+          <t>3161364; 3326987</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3799360; 3968661</t>
+          <t>3797016; 3961862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3483912; 3659063</t>
+          <t>3488953; 3660935</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2972143; 3633796</t>
+          <t>3275867; 3442213</t>
         </is>
       </c>
     </row>
